--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486335_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486335_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.4617</v>
+        <v>8.694900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9346</v>
+        <v>4.7364</v>
       </c>
       <c r="F2" t="n">
-        <v>3.527</v>
+        <v>3.9586</v>
       </c>
       <c r="G2" t="n">
         <v>6.6154</v>
@@ -610,13 +610,13 @@
         <v>1.0875</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7588</v>
+        <v>0.992</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9782</v>
+        <v>0.7799</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2194</v>
+        <v>0.2121</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>X. OROZ URIA</t>
+          <t>A. KUNKEL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2878</v>
+        <v>5.3449</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4268</v>
+        <v>2.2762</v>
       </c>
       <c r="F3" t="n">
-        <v>2.861</v>
+        <v>3.0687</v>
       </c>
       <c r="G3" t="n">
-        <v>3.647</v>
+        <v>3.279</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5449</v>
+        <v>4.0025</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1021</v>
+        <v>-0.7235</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4917</v>
+        <v>2.099</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9671999999999999</v>
+        <v>3.1452</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5245</v>
+        <v>-1.0462</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1553</v>
+        <v>1.18</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5776</v>
+        <v>0.8573</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4224</v>
+        <v>0.3227</v>
       </c>
       <c r="P3" t="n">
+        <v>-2.1751</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-3.2626</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.0875</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-1.0875</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.1751</v>
-      </c>
       <c r="S3" t="n">
-        <v>1.5533</v>
+        <v>0.6558</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0227</v>
+        <v>-0.1454</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.8012</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>3.5851</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.5851</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. KUNKEL</t>
+          <t>X. OROZ URIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3601</v>
+        <v>5.2975</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6921</v>
+        <v>2.868</v>
       </c>
       <c r="F4" t="n">
-        <v>2.668</v>
+        <v>2.4295</v>
       </c>
       <c r="G4" t="n">
-        <v>3.279</v>
+        <v>3.647</v>
       </c>
       <c r="H4" t="n">
-        <v>4.0025</v>
+        <v>1.5449</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7235</v>
+        <v>2.1021</v>
       </c>
       <c r="J4" t="n">
-        <v>2.099</v>
+        <v>3.4917</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1452</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.0462</v>
+        <v>2.5245</v>
       </c>
       <c r="M4" t="n">
-        <v>1.18</v>
+        <v>0.1553</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8573</v>
+        <v>0.5776</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3227</v>
+        <v>-0.4224</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.1751</v>
+        <v>1.0875</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0875</v>
+        <v>2.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3289</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7294</v>
+        <v>0.4639</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4005</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>3.5851</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>3.5851</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6307</v>
+        <v>3.1008</v>
       </c>
       <c r="E5" t="n">
-        <v>2.019</v>
+        <v>2.2425</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6117</v>
+        <v>0.8582</v>
       </c>
       <c r="G5" t="n">
         <v>1.252</v>
@@ -844,13 +844,13 @@
         <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3391</v>
+        <v>0.131</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2499</v>
+        <v>-0.0264</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0892</v>
+        <v>0.1574</v>
       </c>
       <c r="V5" t="n">
         <v>0.1952</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4598</v>
+        <v>2.8589</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3333</v>
+        <v>0.9174</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1265</v>
+        <v>1.9415</v>
       </c>
       <c r="G6" t="n">
         <v>0.5607</v>
@@ -922,13 +922,13 @@
         <v>1.0875</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8116</v>
+        <v>1.2107</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4846</v>
+        <v>1.2996</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. ARMUS</t>
+          <t>M. KAMBA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9243</v>
+        <v>2.2669</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2794</v>
+        <v>-0.0422</v>
       </c>
       <c r="F7" t="n">
-        <v>4.2037</v>
+        <v>2.3091</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4579</v>
+        <v>2.202</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7846</v>
+        <v>1.3501</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3267</v>
+        <v>0.8518</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.8053</v>
+        <v>0.8482</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.9583</v>
+        <v>0.657</v>
       </c>
       <c r="L7" t="n">
-        <v>0.153</v>
+        <v>0.1912</v>
       </c>
       <c r="M7" t="n">
-        <v>1.3474</v>
+        <v>1.3538</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1737</v>
+        <v>0.6932</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1737</v>
+        <v>0.6606</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5225</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>3.7095</v>
+        <v>-0.1097</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5057</v>
+        <v>0.1971</v>
       </c>
       <c r="U7" t="n">
-        <v>2.2038</v>
+        <v>-0.3067</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1952</v>
+        <v>0.1745</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. KAMBA</t>
+          <t>S. UGOCHUKWU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.789</v>
+        <v>1.193</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4893</v>
+        <v>-1.3161</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2783</v>
+        <v>2.5091</v>
       </c>
       <c r="G8" t="n">
-        <v>2.202</v>
+        <v>-0.328</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3501</v>
+        <v>-1.0309</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8518</v>
+        <v>0.7028</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8482</v>
+        <v>-1.0188</v>
       </c>
       <c r="K8" t="n">
-        <v>0.657</v>
+        <v>-1.21</v>
       </c>
       <c r="L8" t="n">
         <v>0.1912</v>
       </c>
       <c r="M8" t="n">
-        <v>1.3538</v>
+        <v>0.6907</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6932</v>
+        <v>0.1792</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6606</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5875</v>
+        <v>-0.4137</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2499</v>
+        <v>0.03</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3376</v>
+        <v>-0.4437</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1745</v>
+        <v>1.4997</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1745</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. UGOCHUKWU</t>
+          <t>A. WINTERING</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8154</v>
+        <v>0.8448</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5396</v>
+        <v>-0.743</v>
       </c>
       <c r="F9" t="n">
-        <v>2.355</v>
+        <v>1.5878</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.328</v>
+        <v>0.2352</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0309</v>
+        <v>3.06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7028</v>
+        <v>-2.8248</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0188</v>
+        <v>-1.0118</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.21</v>
+        <v>1.9868</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1912</v>
+        <v>-2.9985</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6907</v>
+        <v>1.2469</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1792</v>
+        <v>1.0732</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.1737</v>
       </c>
       <c r="P9" t="n">
-        <v>0.435</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7913</v>
+        <v>1.0022</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1935</v>
+        <v>0.1839</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5979</v>
+        <v>0.8183</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4997</v>
+        <v>1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7602</v>
+        <v>2.2599</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7395</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. WINTERING</t>
+          <t>M. ARMUS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,37 +1189,37 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.596</v>
+        <v>0.4082</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9918</v>
+        <v>-3.1482</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5878</v>
+        <v>3.5564</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2352</v>
+        <v>-0.4579</v>
       </c>
       <c r="H10" t="n">
-        <v>3.06</v>
+        <v>-0.7846</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.8248</v>
+        <v>0.3267</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0118</v>
+        <v>-1.8053</v>
       </c>
       <c r="K10" t="n">
-        <v>1.9868</v>
+        <v>-1.9583</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.9985</v>
+        <v>0.153</v>
       </c>
       <c r="M10" t="n">
-        <v>1.2469</v>
+        <v>1.3474</v>
       </c>
       <c r="N10" t="n">
-        <v>1.0732</v>
+        <v>1.1737</v>
       </c>
       <c r="O10" t="n">
         <v>0.1737</v>
@@ -1234,22 +1234,22 @@
         <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7534999999999999</v>
+        <v>2.1934</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0649</v>
+        <v>0.6369</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8183</v>
+        <v>1.5565</v>
       </c>
       <c r="V10" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="W10" t="n">
-        <v>2.2599</v>
+        <v>0.1952</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>29.3248</v>
+        <v>30.0099</v>
       </c>
       <c r="E11" t="n">
-        <v>7.105700000000001</v>
+        <v>7.790999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>22.219</v>
+        <v>22.2189</v>
       </c>
       <c r="G11" t="n">
         <v>17.0054</v>
@@ -1285,13 +1285,13 @@
         <v>7.9726</v>
       </c>
       <c r="J11" t="n">
-        <v>6.8146</v>
+        <v>6.814600000000001</v>
       </c>
       <c r="K11" t="n">
         <v>2.2683</v>
       </c>
       <c r="L11" t="n">
-        <v>4.546200000000001</v>
+        <v>4.5462</v>
       </c>
       <c r="M11" t="n">
         <v>10.1906</v>
@@ -1312,10 +1312,10 @@
         <v>10.8751</v>
       </c>
       <c r="S11" t="n">
-        <v>5.539899999999999</v>
+        <v>6.2247</v>
       </c>
       <c r="T11" t="n">
-        <v>1.3461</v>
+        <v>2.031</v>
       </c>
       <c r="U11" t="n">
         <v>4.1938</v>
@@ -1327,7 +1327,7 @@
         <v>9.820600000000001</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.041</v>
+        <v>-3.040999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.648</v>
+        <v>1.5633</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6488</v>
+        <v>-0.8724</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2968</v>
+        <v>2.4356</v>
       </c>
       <c r="G12" t="n">
         <v>-0.3824</v>
@@ -1390,13 +1390,13 @@
         <v>1.9576</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.882</v>
+        <v>-0.9668</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8868</v>
+        <v>-1.1103</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0048</v>
+        <v>0.1436</v>
       </c>
       <c r="V12" t="n">
         <v>2.2599</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L. NWOGBO</t>
+          <t>A. BRIMAH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1191</v>
+        <v>1.1006</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3654</v>
+        <v>0.489</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2464</v>
+        <v>0.6116</v>
       </c>
       <c r="G13" t="n">
-        <v>0.466</v>
+        <v>1.1006</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0373</v>
+        <v>-0.0731</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5714</v>
+        <v>1.1738</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9402</v>
+        <v>1.037</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9402</v>
+        <v>0.3102</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.7267</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4742</v>
+        <v>0.0636</v>
       </c>
       <c r="N13" t="n">
-        <v>0.09710000000000001</v>
+        <v>-0.3834</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5714</v>
+        <v>0.447</v>
       </c>
       <c r="P13" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6956</v>
+        <v>-0.435</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4252</v>
+        <v>-0.548</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7297</v>
+        <v>0.113</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. BRIMAH</t>
+          <t>L. NWOGBO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1006</v>
+        <v>0.8069</v>
       </c>
       <c r="E14" t="n">
-        <v>0.489</v>
+        <v>1.3596</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6116</v>
+        <v>-0.5527</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1006</v>
+        <v>0.466</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0731</v>
+        <v>1.0373</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1738</v>
+        <v>-0.5714</v>
       </c>
       <c r="J14" t="n">
-        <v>1.037</v>
+        <v>0.9402</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3102</v>
+        <v>0.9402</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7267</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0636</v>
+        <v>-0.4742</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3834</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>0.447</v>
+        <v>-0.5714</v>
       </c>
       <c r="P14" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.435</v>
+        <v>0.3833</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.548</v>
+        <v>0.4194</v>
       </c>
       <c r="U14" t="n">
-        <v>0.113</v>
+        <v>-0.0361</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1069</v>
+        <v>0.6047</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.8042</v>
+        <v>-0.5807</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6973</v>
+        <v>1.1854</v>
       </c>
       <c r="G15" t="n">
         <v>2.2671</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5465</v>
+        <v>-0.8349</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9469</v>
+        <v>-0.7234</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5995</v>
+        <v>-0.1115</v>
       </c>
       <c r="V15" t="n">
         <v>1.13</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.4618</v>
+        <v>-2.2575</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.4557</v>
+        <v>-3.344</v>
       </c>
       <c r="F16" t="n">
-        <v>0.994</v>
+        <v>1.0864</v>
       </c>
       <c r="G16" t="n">
         <v>-0.9769</v>
@@ -1702,13 +1702,13 @@
         <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0944</v>
+        <v>-0.8902</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2329</v>
+        <v>-1.1212</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1385</v>
+        <v>0.231</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3904</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.5988</v>
+        <v>-3.0882</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.5552</v>
+        <v>-1.8905</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0436</v>
+        <v>-1.1977</v>
       </c>
       <c r="G17" t="n">
         <v>-1.4401</v>
@@ -1780,13 +1780,13 @@
         <v>0.6525</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2758</v>
+        <v>-0.2136</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0721</v>
+        <v>-0.2632</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2037</v>
+        <v>0.0496</v>
       </c>
       <c r="V17" t="n">
         <v>-1.8695</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.8845</v>
+        <v>-3.239</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1013</v>
+        <v>-1.5483</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7832</v>
+        <v>-1.6907</v>
       </c>
       <c r="G18" t="n">
         <v>-2.8762</v>
@@ -1858,13 +1858,13 @@
         <v>0.2175</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3392</v>
+        <v>-0.0153</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2776</v>
+        <v>-0.1694</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0616</v>
+        <v>0.1541</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5649999999999999</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. VAULET</t>
+          <t>P. GARINO GULLOTTA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.6826</v>
+        <v>-3.7864</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.799</v>
+        <v>-4.0135</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8836000000000001</v>
+        <v>0.2271</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.1504</v>
+        <v>-3.0258</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.9352</v>
+        <v>-1.2743</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2152</v>
+        <v>-1.7515</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.6641</v>
+        <v>-3.4631</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.8498</v>
+        <v>-1.3044</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1857</v>
+        <v>-2.1587</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4863</v>
+        <v>0.4373</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0854</v>
+        <v>0.0302</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4009</v>
+        <v>0.4072</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2175</v>
+        <v>1.5225</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6201</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6922</v>
+        <v>-0.5504</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0721</v>
+        <v>-0.0379</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9347</v>
+        <v>-1.695</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1952</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. GARINO GULLOTTA</t>
+          <t>J. VAULET</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.7191</v>
+        <v>-4.879</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.684</v>
+        <v>-4.1343</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.035</v>
+        <v>-0.7448</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.0258</v>
+        <v>-4.1504</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2743</v>
+        <v>-3.9352</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7515</v>
+        <v>-0.2152</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.4631</v>
+        <v>-2.6641</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3044</v>
+        <v>-3.8498</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.1587</v>
+        <v>1.1857</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4373</v>
+        <v>-1.4863</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0302</v>
+        <v>-0.0854</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4072</v>
+        <v>-1.4009</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5225</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5209</v>
+        <v>0.4236</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2209</v>
+        <v>0.3569</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3</v>
+        <v>0.0667</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.695</v>
+        <v>-0.9347</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.695</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.8686</v>
+        <v>-5.7767</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.5876</v>
+        <v>-3.917</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.281</v>
+        <v>-1.8597</v>
       </c>
       <c r="G21" t="n">
         <v>-4.0483</v>
@@ -2092,13 +2092,13 @@
         <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4728</v>
+        <v>-0.3809</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2209</v>
+        <v>-0.5504</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2519</v>
+        <v>0.1694</v>
       </c>
       <c r="V21" t="n">
         <v>-1.13</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.8703</v>
+        <v>-8.1381</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.4374</v>
+        <v>-3.7669</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.4329</v>
+        <v>-4.3712</v>
       </c>
       <c r="G22" t="n">
         <v>-3.9387</v>
@@ -2170,13 +2170,13 @@
         <v>0.435</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5189</v>
+        <v>0.2133</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6044</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0856</v>
+        <v>0.1472</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4552</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-29.3249</v>
+        <v>-27.0894</v>
       </c>
       <c r="E23" t="n">
-        <v>-22.2188</v>
+        <v>-22.219</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.106</v>
+        <v>-4.8707</v>
       </c>
       <c r="G23" t="n">
         <v>-17.0051</v>
@@ -2224,7 +2224,7 @@
         <v>-10.1906</v>
       </c>
       <c r="K23" t="n">
-        <v>-6.7644</v>
+        <v>-6.764400000000001</v>
       </c>
       <c r="L23" t="n">
         <v>-3.4264</v>
@@ -2239,7 +2239,7 @@
         <v>-4.5464</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.000199999999999978</v>
+        <v>-0.0002000000000004221</v>
       </c>
       <c r="Q23" t="n">
         <v>-10.8752</v>
@@ -2248,13 +2248,13 @@
         <v>10.8751</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.539800000000001</v>
+        <v>-3.3047</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.193700000000001</v>
+        <v>-4.1939</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.346</v>
+        <v>0.8891</v>
       </c>
       <c r="V23" t="n">
         <v>-6.7799</v>
